--- a/BoutiquePath_Revenue_Model_v2.xlsx
+++ b/BoutiquePath_Revenue_Model_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SolFound\BoutiquePath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04e9bb415d956f31/Desktop/solfound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA37ED3-52D7-4475-928F-39BD91520286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CEA37ED3-52D7-4475-928F-39BD91520286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5AB1095-3CDD-4F96-AFA9-535C168260F1}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-105" windowWidth="29040" windowHeight="15720" tabRatio="812" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17070" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="812" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="308">
   <si>
     <t>⚙️  UNIVERSAL REVENUE MODEL v3 — INPUTS</t>
   </si>
@@ -524,18 +524,12 @@
     <t>3D Filament</t>
   </si>
   <si>
-    <t>$/oz</t>
-  </si>
-  <si>
     <t>oz</t>
   </si>
   <si>
     <t>g</t>
   </si>
   <si>
-    <t>cog</t>
-  </si>
-  <si>
     <t>3D Shell Mug 1</t>
   </si>
   <si>
@@ -548,21 +542,6 @@
     <t>3D Pencil Coozie</t>
   </si>
   <si>
-    <t>PLA Basic</t>
-  </si>
-  <si>
-    <t>PLA Matte</t>
-  </si>
-  <si>
-    <t>PLA Silk</t>
-  </si>
-  <si>
-    <t>PLA Translucent</t>
-  </si>
-  <si>
-    <t>Cost of Fillament</t>
-  </si>
-  <si>
     <t>PLA</t>
   </si>
   <si>
@@ -686,9 +665,6 @@
     <t>Industrial, chemical‑resistant parts</t>
   </si>
   <si>
-    <t>💲  COG — Update Weekly/Monthy for Use in Pricing</t>
-  </si>
-  <si>
     <t>Material Type</t>
   </si>
   <si>
@@ -890,24 +866,6 @@
     <t>per oz</t>
   </si>
   <si>
-    <t>small</t>
-  </si>
-  <si>
-    <t>mid</t>
-  </si>
-  <si>
-    <t>large</t>
-  </si>
-  <si>
-    <t>hours</t>
-  </si>
-  <si>
-    <t># products made</t>
-  </si>
-  <si>
-    <t>total hrs</t>
-  </si>
-  <si>
     <t>$0.02/hr * 40 hr/wk printing * 4.2 wk/mo</t>
   </si>
   <si>
@@ -1029,6 +987,9 @@
   </si>
   <si>
     <t>3D Bow</t>
+  </si>
+  <si>
+    <t>💲  Raw Material Cost — Update Weekly/Monthy for Use in Pricing</t>
   </si>
 </sst>
 </file>
@@ -1634,36 +1595,12 @@
     <xf numFmtId="9" fontId="7" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1671,6 +1608,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1678,7 +1617,13 @@
     <xf numFmtId="0" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1710,6 +1655,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2958,6 +2919,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3257,18 +3222,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
+      <c r="A1" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
     </row>
     <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -3282,11 +3247,11 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -3333,11 +3298,11 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="93"/>
     </row>
     <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
@@ -3362,11 +3327,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="89"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -3392,11 +3357,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101" t="s">
+      <c r="A15" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="93"/>
     </row>
     <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
@@ -3410,11 +3375,11 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="102" t="s">
+      <c r="A18" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3448,33 +3413,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
       <c r="G2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="H2" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="I2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="J2" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -3496,13 +3461,13 @@
       <c r="I3" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="93"/>
       <c r="I4" s="58"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -3545,7 +3510,7 @@
         <v>46142</v>
       </c>
       <c r="H6" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="I6" s="58">
         <v>69.7</v>
@@ -3605,7 +3570,7 @@
         <v>46146</v>
       </c>
       <c r="H8" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="I8" s="58">
         <v>50.87</v>
@@ -3635,7 +3600,7 @@
         <v>46147</v>
       </c>
       <c r="H9" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="I9" s="58">
         <f>207.39*1.0825</f>
@@ -3666,7 +3631,7 @@
         <v>46147</v>
       </c>
       <c r="H10" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="I10" s="58">
         <f>7.88*1.0825</f>
@@ -3677,7 +3642,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="96" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="72">
@@ -3691,7 +3656,7 @@
         <v>46147</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="I11" s="58">
         <f>5.29*1.0825</f>
@@ -3702,18 +3667,18 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="89"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
       <c r="G12" s="57">
         <v>46147</v>
       </c>
       <c r="H12" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="I12" s="58">
         <f>10.49*1.0825</f>
@@ -3725,7 +3690,7 @@
     </row>
     <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="63" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B13" s="64">
         <f>0.02*80*4.2</f>
@@ -3739,7 +3704,7 @@
         <v>0.19399538106235567</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -3757,12 +3722,12 @@
         <v>4.3302540415704387</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="63" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B15" s="64">
         <v>8.5299999999999994</v>
@@ -3780,7 +3745,7 @@
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="63" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B16" s="64">
         <v>5.73</v>
@@ -3791,7 +3756,7 @@
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="63" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B17" s="64">
         <v>10</v>
@@ -3832,26 +3797,26 @@
     </row>
     <row r="20" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="89"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
       <c r="F21" s="48">
         <f>B11</f>
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="89"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="93"/>
       <c r="F22" s="49">
         <f>B19</f>
         <v>192.33999999999997</v>
@@ -3859,13 +3824,13 @@
     </row>
     <row r="23" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="89"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="93"/>
       <c r="F24" s="50">
         <f>F21+F22</f>
         <v>252.33999999999997</v>
@@ -3873,32 +3838,32 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H25" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H26" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H27" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H28" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H29" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H30" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3937,37 +3902,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="M1" s="109" t="s">
-        <v>211</v>
-      </c>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
+      <c r="A1" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="M1" s="103" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="M2">
         <v>1</v>
       </c>
@@ -3976,42 +3941,42 @@
         <v>3.5274E-2</v>
       </c>
       <c r="O2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="I3" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="J3" s="54" t="s">
+        <v>245</v>
+      </c>
+      <c r="K3" s="54" t="s">
         <v>202</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I3" s="54" t="s">
-        <v>209</v>
-      </c>
-      <c r="J3" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="K3" s="54" t="s">
-        <v>210</v>
       </c>
       <c r="M3">
         <v>28.349399999999999</v>
@@ -4020,33 +3985,33 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="110" t="s">
-        <v>165</v>
+      <c r="A4" s="104" t="s">
+        <v>158</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I4" s="3">
         <v>12.99</v>
@@ -4061,7 +4026,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="111"/>
+      <c r="A5" s="105"/>
       <c r="B5" s="23"/>
       <c r="C5" s="24"/>
       <c r="D5" s="25"/>
@@ -4069,7 +4034,7 @@
       <c r="F5" s="25"/>
       <c r="G5" s="26"/>
       <c r="H5" s="55" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I5" s="3">
         <v>12.99</v>
@@ -4084,7 +4049,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="111"/>
+      <c r="A6" s="105"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="25"/>
@@ -4092,7 +4057,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="26"/>
       <c r="H6" s="55" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="I6" s="3">
         <v>12.99</v>
@@ -4107,7 +4072,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="111"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="25"/>
@@ -4115,7 +4080,7 @@
       <c r="F7" s="25"/>
       <c r="G7" s="26"/>
       <c r="H7" s="55" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="I7" s="3">
         <v>14.94</v>
@@ -4130,7 +4095,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="111"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="23"/>
       <c r="C8" s="24"/>
       <c r="D8" s="25"/>
@@ -4138,7 +4103,7 @@
       <c r="F8" s="25"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I8" s="3">
         <v>20.99</v>
@@ -4153,7 +4118,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="111"/>
+      <c r="A9" s="105"/>
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
       <c r="D9" s="25"/>
@@ -4161,7 +4126,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="26"/>
       <c r="H9" s="26" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I9" s="3">
         <f>65.99/4</f>
@@ -4180,11 +4145,11 @@
         <v>13.686428571428573</v>
       </c>
       <c r="O9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="111"/>
+      <c r="A10" s="105"/>
       <c r="B10" s="23"/>
       <c r="C10" s="24"/>
       <c r="D10" s="25"/>
@@ -4192,7 +4157,7 @@
       <c r="F10" s="25"/>
       <c r="G10" s="26"/>
       <c r="H10" s="26" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I10" s="3">
         <f>65.99/4</f>
@@ -4211,11 +4176,11 @@
         <v>1.3686428571428573E-2</v>
       </c>
       <c r="O10" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="111"/>
+      <c r="A11" s="105"/>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
       <c r="D11" s="25"/>
@@ -4223,7 +4188,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I11" s="3">
         <v>24.99</v>
@@ -4241,11 +4206,11 @@
         <v>0.38787338571428576</v>
       </c>
       <c r="O11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="111"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="23"/>
       <c r="C12" s="24"/>
       <c r="D12" s="25"/>
@@ -4253,7 +4218,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="I12" s="3">
         <v>31.99</v>
@@ -4268,7 +4233,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="111"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="23"/>
       <c r="C13" s="24"/>
       <c r="D13" s="25"/>
@@ -4276,7 +4241,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I13" s="3">
         <v>24.99</v>
@@ -4291,7 +4256,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="111"/>
+      <c r="A14" s="105"/>
       <c r="B14" s="23"/>
       <c r="C14" s="24"/>
       <c r="D14" s="25"/>
@@ -4299,7 +4264,7 @@
       <c r="F14" s="25"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I14" s="3">
         <v>24.99</v>
@@ -4314,7 +4279,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="111"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
       <c r="D15" s="25"/>
@@ -4322,7 +4287,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I15" s="3">
         <v>24.99</v>
@@ -4337,7 +4302,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="111"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="23"/>
       <c r="C16" s="24"/>
       <c r="D16" s="25"/>
@@ -4345,7 +4310,7 @@
       <c r="F16" s="25"/>
       <c r="G16" s="26"/>
       <c r="H16" s="26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I16" s="3">
         <v>24.99</v>
@@ -4360,7 +4325,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="111"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
       <c r="D17" s="25"/>
@@ -4368,7 +4333,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="26"/>
       <c r="H17" s="26" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I17" s="3">
         <v>24.99</v>
@@ -4383,7 +4348,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="111"/>
+      <c r="A18" s="105"/>
       <c r="B18" s="23"/>
       <c r="C18" s="24"/>
       <c r="D18" s="25"/>
@@ -4391,7 +4356,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="26"/>
       <c r="H18" s="26" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I18" s="3">
         <v>24.99</v>
@@ -4406,7 +4371,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="111"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
       <c r="D19" s="25"/>
@@ -4414,7 +4379,7 @@
       <c r="F19" s="25"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I19" s="3">
         <v>24.99</v>
@@ -4429,7 +4394,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="111"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24"/>
       <c r="D20" s="25"/>
@@ -4437,7 +4402,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="26"/>
       <c r="H20" s="26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I20" s="3">
         <v>44.99</v>
@@ -4452,7 +4417,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="112"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="23"/>
       <c r="C21" s="24"/>
       <c r="D21" s="25"/>
@@ -4471,29 +4436,29 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="113" t="s">
-        <v>172</v>
+      <c r="A22" s="107" t="s">
+        <v>165</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="I22" s="3">
         <v>12.99</v>
@@ -4508,7 +4473,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115"/>
+      <c r="A23" s="109"/>
       <c r="B23" s="31"/>
       <c r="C23" s="32"/>
       <c r="D23" s="33"/>
@@ -4516,7 +4481,7 @@
       <c r="F23" s="33"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I23" s="3">
         <v>12.99</v>
@@ -4531,7 +4496,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="115"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="31"/>
       <c r="C24" s="32"/>
       <c r="D24" s="33"/>
@@ -4539,7 +4504,7 @@
       <c r="F24" s="33"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I24" s="3">
         <v>12.99</v>
@@ -4554,7 +4519,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="115"/>
+      <c r="A25" s="109"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32"/>
       <c r="D25" s="33"/>
@@ -4562,7 +4527,7 @@
       <c r="F25" s="33"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I25" s="3">
         <v>31.99</v>
@@ -4577,7 +4542,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="114"/>
+      <c r="A26" s="108"/>
       <c r="B26" s="31"/>
       <c r="C26" s="32"/>
       <c r="D26" s="33"/>
@@ -4596,29 +4561,29 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="110" t="s">
-        <v>179</v>
+      <c r="A27" s="104" t="s">
+        <v>172</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I27" s="3">
         <v>12.99</v>
@@ -4633,7 +4598,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="111"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="23"/>
       <c r="C28" s="24"/>
       <c r="D28" s="25"/>
@@ -4641,7 +4606,7 @@
       <c r="F28" s="25"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I28" s="3">
         <v>29.9</v>
@@ -4656,7 +4621,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="111"/>
+      <c r="A29" s="105"/>
       <c r="B29" s="23"/>
       <c r="C29" s="24"/>
       <c r="D29" s="25"/>
@@ -4664,7 +4629,7 @@
       <c r="F29" s="25"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I29" s="3">
         <v>36.9</v>
@@ -4679,7 +4644,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="112"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="23"/>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
@@ -4698,29 +4663,29 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="113" t="s">
-        <v>184</v>
+      <c r="A31" s="107" t="s">
+        <v>177</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I31" s="3">
         <v>29.99</v>
@@ -4735,7 +4700,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="115"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32"/>
       <c r="D32" s="33"/>
@@ -4743,7 +4708,7 @@
       <c r="F32" s="33"/>
       <c r="G32" s="34"/>
       <c r="H32" s="34" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I32" s="3">
         <v>49.99</v>
@@ -4758,7 +4723,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="115"/>
+      <c r="A33" s="109"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32"/>
       <c r="D33" s="33"/>
@@ -4766,7 +4731,7 @@
       <c r="F33" s="33"/>
       <c r="G33" s="34"/>
       <c r="H33" s="34" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I33" s="3">
         <v>36.99</v>
@@ -4781,7 +4746,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="114"/>
+      <c r="A34" s="108"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32"/>
       <c r="D34" s="33"/>
@@ -4800,29 +4765,29 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="110" t="s">
-        <v>187</v>
+      <c r="A35" s="104" t="s">
+        <v>180</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I35" s="3">
         <v>34.99</v>
@@ -4837,17 +4802,17 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="111"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="23"/>
       <c r="C36" s="24"/>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
       <c r="G36" s="26" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I36" s="3">
         <v>41.99</v>
@@ -4862,17 +4827,17 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="111"/>
+      <c r="A37" s="105"/>
       <c r="B37" s="23"/>
       <c r="C37" s="24"/>
       <c r="D37" s="25"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
       <c r="G37" s="26" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I37" s="3">
         <v>41.99</v>
@@ -4887,7 +4852,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="112"/>
+      <c r="A38" s="106"/>
       <c r="B38" s="23"/>
       <c r="C38" s="24"/>
       <c r="D38" s="25"/>
@@ -4906,29 +4871,29 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113" t="s">
-        <v>190</v>
+      <c r="A39" s="107" t="s">
+        <v>183</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H39" s="34" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="I39" s="3">
         <v>39.99</v>
@@ -4943,17 +4908,17 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="115"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32"/>
       <c r="D40" s="33"/>
       <c r="E40" s="33"/>
       <c r="F40" s="33"/>
       <c r="G40" s="34" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I40" s="3">
         <v>54.99</v>
@@ -4968,7 +4933,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32"/>
       <c r="D41" s="33"/>
@@ -4987,29 +4952,29 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="110" t="s">
-        <v>193</v>
+      <c r="A42" s="104" t="s">
+        <v>186</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I42" s="3">
         <v>42.99</v>
@@ -5024,7 +4989,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="111"/>
+      <c r="A43" s="105"/>
       <c r="B43" s="23"/>
       <c r="C43" s="24"/>
       <c r="D43" s="25"/>
@@ -5032,7 +4997,7 @@
       <c r="F43" s="25"/>
       <c r="G43" s="26"/>
       <c r="H43" s="26" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I43" s="3">
         <v>59.99</v>
@@ -5047,7 +5012,7 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="112"/>
+      <c r="A44" s="106"/>
       <c r="B44" s="23"/>
       <c r="C44" s="24"/>
       <c r="D44" s="25"/>
@@ -5066,29 +5031,29 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="113" t="s">
-        <v>195</v>
+      <c r="A45" s="107" t="s">
+        <v>188</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F45" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="G45" s="34" t="s">
-        <v>205</v>
-      </c>
       <c r="H45" s="34" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I45" s="3">
         <v>129.99</v>
@@ -5103,7 +5068,7 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="114"/>
+      <c r="A46" s="108"/>
       <c r="B46" s="31"/>
       <c r="C46" s="32"/>
       <c r="D46" s="33"/>
@@ -5122,8 +5087,8 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="106" t="s">
-        <v>306</v>
+      <c r="A47" s="100" t="s">
+        <v>292</v>
       </c>
       <c r="B47" s="77"/>
       <c r="C47" s="78"/>
@@ -5132,7 +5097,7 @@
       <c r="F47" s="79"/>
       <c r="G47" s="55"/>
       <c r="H47" s="55" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="I47" s="64">
         <f>19.99*(1000/350)</f>
@@ -5147,11 +5112,11 @@
         <v>1.6191557314285714</v>
       </c>
       <c r="M47" s="85" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="107"/>
+      <c r="A48" s="101"/>
       <c r="B48" s="77"/>
       <c r="C48" s="78"/>
       <c r="D48" s="79"/>
@@ -5159,7 +5124,7 @@
       <c r="F48" s="79"/>
       <c r="G48" s="55"/>
       <c r="H48" s="55" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="I48" s="64">
         <f>19.99*(1000/350)</f>
@@ -5174,11 +5139,11 @@
         <v>1.6191557314285714</v>
       </c>
       <c r="M48" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="107"/>
+      <c r="A49" s="101"/>
       <c r="B49" s="77"/>
       <c r="C49" s="78"/>
       <c r="D49" s="79"/>
@@ -5186,7 +5151,7 @@
       <c r="F49" s="79"/>
       <c r="G49" s="55"/>
       <c r="H49" s="55" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="I49" s="64">
         <f>24.99*(1000/350)</f>
@@ -5202,7 +5167,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="108"/>
+      <c r="A50" s="102"/>
       <c r="B50" s="77"/>
       <c r="C50" s="78"/>
       <c r="D50" s="79"/>
@@ -5210,7 +5175,7 @@
       <c r="F50" s="79"/>
       <c r="G50" s="55"/>
       <c r="H50" s="55" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="I50" s="64">
         <f>39.99*(1000/350)</f>
@@ -5930,7 +5895,7 @@
   <sheetPr>
     <tabColor rgb="FF2E7D52"/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.7265625" bestFit="1" customWidth="1"/>
@@ -5946,47 +5911,35 @@
     <col min="14" max="14" width="15.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="R1">
-        <v>1</v>
-      </c>
-      <c r="S1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+    </row>
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="R2">
-        <v>28.34</v>
-      </c>
-      <c r="S2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+    </row>
+    <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
@@ -5994,10 +5947,10 @@
         <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>63</v>
@@ -6017,20 +5970,12 @@
       <c r="J3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="O3" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q3" s="51" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+    </row>
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>148</v>
       </c>
@@ -6038,7 +5983,7 @@
         <v>147</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D4" s="15">
         <v>15.5</v>
@@ -6056,36 +6001,18 @@
         <v>1</v>
       </c>
       <c r="J4" s="21"/>
-      <c r="K4" t="s">
-        <v>254</v>
-      </c>
-      <c r="M4" t="s">
-        <v>165</v>
-      </c>
-      <c r="N4" t="s">
-        <v>160</v>
-      </c>
-      <c r="O4" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="P4">
-        <f>15.5*(1/R2)</f>
-        <v>0.54693013408609747</v>
-      </c>
-      <c r="Q4" s="52">
-        <f>O4*P4</f>
-        <v>0.27346506704304874</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O4" s="52"/>
+      <c r="Q4" s="52"/>
+    </row>
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D5" s="15">
         <v>15.5</v>
@@ -6103,26 +6030,18 @@
         <v>1</v>
       </c>
       <c r="J5" s="21"/>
-      <c r="K5" t="s">
+      <c r="O5" s="52"/>
+      <c r="Q5" s="52"/>
+    </row>
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="N5" t="s">
-        <v>161</v>
-      </c>
-      <c r="O5" s="52">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="52"/>
-    </row>
-    <row r="6" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
-        <v>263</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D6" s="15">
         <v>15.5</v>
@@ -6140,22 +6059,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="21"/>
-      <c r="K6" t="s">
-        <v>256</v>
-      </c>
-      <c r="N6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D7" s="15">
         <v>15.5</v>
@@ -6173,14 +6086,8 @@
         <v>0</v>
       </c>
       <c r="J7" s="21"/>
-      <c r="K7" t="s">
-        <v>257</v>
-      </c>
-      <c r="N7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>149</v>
       </c>
@@ -6188,7 +6095,7 @@
         <v>147</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D8" s="15">
         <v>29.9</v>
@@ -6206,19 +6113,16 @@
         <v>1</v>
       </c>
       <c r="J8" s="21"/>
-      <c r="K8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D9" s="15">
         <v>29.9</v>
@@ -6236,19 +6140,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="21"/>
-      <c r="K9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D10" s="15">
         <v>29.9</v>
@@ -6267,15 +6168,15 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D11" s="15">
         <v>15.5</v>
@@ -6295,15 +6196,15 @@
       <c r="J11" s="21"/>
       <c r="K11" s="56"/>
     </row>
-    <row r="12" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D12" s="15">
         <v>15.5</v>
@@ -6323,15 +6224,15 @@
       <c r="J12" s="21"/>
       <c r="K12" s="56"/>
     </row>
-    <row r="13" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D13" s="15">
         <v>29.12</v>
@@ -6349,25 +6250,16 @@
         <v>2</v>
       </c>
       <c r="J13" s="21"/>
-      <c r="M13" t="s">
-        <v>277</v>
-      </c>
-      <c r="N13" t="s">
-        <v>278</v>
-      </c>
-      <c r="O13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D14" s="15">
         <v>29.12</v>
@@ -6385,29 +6277,16 @@
         <v>2</v>
       </c>
       <c r="J14" s="21"/>
-      <c r="L14" t="s">
-        <v>274</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>5</v>
-      </c>
-      <c r="O14">
-        <f>M14*N14</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D15" s="15">
         <v>183</v>
@@ -6425,29 +6304,16 @@
         <v>5</v>
       </c>
       <c r="J15" s="21"/>
-      <c r="L15" t="s">
-        <v>275</v>
-      </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-      <c r="N15">
-        <v>5</v>
-      </c>
-      <c r="O15">
-        <f>M15*N15</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D16" s="15">
         <v>183</v>
@@ -6465,29 +6331,16 @@
         <v>5</v>
       </c>
       <c r="J16" s="21"/>
-      <c r="L16" t="s">
-        <v>276</v>
-      </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <f>M16*N16</f>
-        <v>15</v>
-      </c>
     </row>
     <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D17" s="15">
         <v>102</v>
@@ -6508,13 +6361,13 @@
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D18" s="15">
         <v>102</v>
@@ -6535,13 +6388,13 @@
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D19" s="15">
         <v>44</v>
@@ -6562,13 +6415,13 @@
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D20" s="15">
         <v>762</v>
@@ -6589,13 +6442,13 @@
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="59" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B21" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D21" s="60">
         <v>4</v>
@@ -6614,13 +6467,13 @@
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="59" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B22" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D22" s="60">
         <v>17</v>
@@ -6639,13 +6492,13 @@
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="59" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="B23" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D23" s="60">
         <v>5</v>
@@ -6664,13 +6517,13 @@
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="59" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B24" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D24" s="60">
         <v>3</v>
@@ -6689,13 +6542,13 @@
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="59" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="B25" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D25" s="60">
         <v>214.54</v>
@@ -6714,13 +6567,13 @@
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="59" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="D26" s="15">
         <v>144</v>
@@ -6739,13 +6592,13 @@
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="59" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B27" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="D27" s="15">
         <v>44</v>
@@ -6764,13 +6617,13 @@
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="59" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B28" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="D28" s="15">
         <v>44</v>
@@ -6789,13 +6642,13 @@
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="59" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B29" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D29" s="15">
         <v>106</v>
@@ -6814,13 +6667,13 @@
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D30" s="15">
         <v>35</v>
@@ -6839,13 +6692,13 @@
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="59" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B31" s="60" t="s">
         <v>147</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D31" s="15">
         <v>42</v>
@@ -6864,13 +6717,13 @@
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D32" s="15">
         <v>59</v>
@@ -6889,13 +6742,13 @@
     </row>
     <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D33" s="15">
         <v>76</v>
@@ -6914,13 +6767,13 @@
     </row>
     <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D34" s="15">
         <v>38</v>
@@ -6939,13 +6792,13 @@
     </row>
     <row r="35" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D35" s="15">
         <v>11</v>
@@ -6964,13 +6817,13 @@
     </row>
     <row r="36" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D36" s="15">
         <v>11</v>
@@ -6989,13 +6842,13 @@
     </row>
     <row r="37" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D37" s="15">
         <v>557.75</v>
@@ -7014,13 +6867,13 @@
     </row>
     <row r="38" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>147</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D38" s="15">
         <v>157.99</v>
@@ -7323,38 +7176,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
     </row>
     <row r="3" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9892,26 +9745,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11334,157 +11187,157 @@
     </row>
     <row r="51" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="88"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="90">
+      <c r="B52" s="92"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="110">
         <f>SUMIF(A4:A50,"&lt;&gt;",D4:D50)</f>
         <v>922.4454869187681</v>
       </c>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="89"/>
+      <c r="E52" s="92"/>
+      <c r="F52" s="92"/>
+      <c r="G52" s="93"/>
     </row>
     <row r="53" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="87" t="s">
+      <c r="A53" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="B53" s="88"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="90">
+      <c r="B53" s="92"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="110">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)</f>
         <v>379.83049461361048</v>
       </c>
-      <c r="E53" s="88"/>
-      <c r="F53" s="88"/>
-      <c r="G53" s="89"/>
+      <c r="E53" s="92"/>
+      <c r="F53" s="92"/>
+      <c r="G53" s="93"/>
     </row>
     <row r="54" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="B54" s="88"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="90">
+      <c r="B54" s="92"/>
+      <c r="C54" s="93"/>
+      <c r="D54" s="110">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)*4.33</f>
         <v>1644.6660416769334</v>
       </c>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="89"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="93"/>
     </row>
     <row r="55" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="93"/>
-      <c r="B55" s="94"/>
-      <c r="C55" s="94"/>
-      <c r="D55" s="94"/>
-      <c r="E55" s="94"/>
-      <c r="F55" s="94"/>
-      <c r="G55" s="94"/>
+      <c r="A55" s="112"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
     </row>
     <row r="56" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="92" t="s">
+      <c r="A56" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="88"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="91">
+      <c r="B56" s="92"/>
+      <c r="C56" s="93"/>
+      <c r="D56" s="111">
         <f>Inputs!B11</f>
         <v>800</v>
       </c>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="89"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="93"/>
     </row>
     <row r="57" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="92" t="s">
+      <c r="A57" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="88"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="91">
+      <c r="B57" s="92"/>
+      <c r="C57" s="93"/>
+      <c r="D57" s="111">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)-Inputs!B11</f>
         <v>-420.16950538638952</v>
       </c>
-      <c r="E57" s="88"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="89"/>
+      <c r="E57" s="92"/>
+      <c r="F57" s="92"/>
+      <c r="G57" s="93"/>
     </row>
     <row r="58" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="93"/>
-      <c r="B58" s="94"/>
-      <c r="C58" s="94"/>
-      <c r="D58" s="94"/>
-      <c r="E58" s="94"/>
-      <c r="F58" s="94"/>
-      <c r="G58" s="94"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="88"/>
+      <c r="C58" s="88"/>
+      <c r="D58" s="88"/>
+      <c r="E58" s="88"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="88"/>
     </row>
     <row r="59" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="88"/>
-      <c r="C59" s="89"/>
-      <c r="D59" s="98" t="e">
+      <c r="B59" s="92"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="114" t="e">
         <f>SUMPRODUCT((A4:A50&lt;&gt;"")*Products!I4:I54*IFERROR(Pricing!C4:C50*1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="89"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
+      <c r="G59" s="93"/>
     </row>
     <row r="60" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="92" t="s">
+      <c r="A60" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="B60" s="88"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="98">
+      <c r="B60" s="92"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="114">
         <f>Inputs!B10</f>
         <v>20</v>
       </c>
-      <c r="E60" s="88"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="89"/>
+      <c r="E60" s="92"/>
+      <c r="F60" s="92"/>
+      <c r="G60" s="93"/>
     </row>
     <row r="61" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="93"/>
-      <c r="B61" s="94"/>
-      <c r="C61" s="94"/>
-      <c r="D61" s="94"/>
-      <c r="E61" s="94"/>
-      <c r="F61" s="94"/>
-      <c r="G61" s="94"/>
+      <c r="A61" s="112"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="88"/>
     </row>
     <row r="62" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="99" t="s">
+      <c r="A62" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="B62" s="88"/>
-      <c r="C62" s="89"/>
-      <c r="D62" s="97">
+      <c r="B62" s="92"/>
+      <c r="C62" s="93"/>
+      <c r="D62" s="113">
         <f>SUMIF(A4:A50,"&lt;&gt;",D4:D50)*4.33*Inputs!B16</f>
         <v>599.12834375373984</v>
       </c>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="89"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="93"/>
     </row>
     <row r="63" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="B63" s="88"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="90">
+      <c r="B63" s="92"/>
+      <c r="C63" s="93"/>
+      <c r="D63" s="110">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)*4.33*(1-Inputs!B16)</f>
         <v>1397.9661354253933</v>
       </c>
-      <c r="E63" s="88"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="89"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -11538,24 +11391,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11578,14 +11431,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="93"/>
     </row>
     <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
@@ -11628,14 +11481,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="89"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="93"/>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
@@ -11813,10 +11666,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="94"/>
+      <c r="B1" s="88"/>
     </row>
     <row r="3" spans="1:2" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="44" t="s">
